--- a/templates/quotation-template.xlsx
+++ b/templates/quotation-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pawan\Documents\Codex\ReshmaSutra\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67A87B1-24B4-41F6-8E0F-EA4A6FB8F224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE5E237-77A1-4E19-B64F-1654AF080F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="jha (2)" sheetId="3" r:id="rId1"/>
@@ -33,9 +33,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -618,7 +615,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -784,13 +781,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -812,35 +802,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -848,7 +813,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -895,15 +860,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1472647</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>83433</xdr:rowOff>
+      <xdr:colOff>1544430</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>17171</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>515177</xdr:colOff>
+      <xdr:colOff>586960</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>7787</xdr:rowOff>
+      <xdr:rowOff>140308</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -937,8 +902,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1844122" y="512058"/>
-          <a:ext cx="1412598" cy="876854"/>
+          <a:off x="1930952" y="630084"/>
+          <a:ext cx="1527312" cy="879615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1781,33 +1746,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="13.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.54296875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="13.26953125" style="1" customWidth="1"/>
     <col min="6" max="6" width="7" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16363" width="9" style="1"/>
-    <col min="16364" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <col min="16364" max="16384" width="9.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+    <row r="1" spans="1:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="100"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="86"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1816,97 +1781,84 @@
       <c r="D2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="92"/>
+      <c r="E2" s="79"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
+      <c r="D3" s="72"/>
+      <c r="E3"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
       <c r="H3" s="10"/>
       <c r="I3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
       <c r="H4" s="10"/>
       <c r="I4"/>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
+      <c r="D5" s="72"/>
+      <c r="E5"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
       <c r="H5" s="10"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
+      <c r="D6" s="72"/>
+      <c r="E6"/>
       <c r="H6" s="10"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="74"/>
       <c r="D7" s="14"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="74"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="18"/>
       <c r="H7" s="10"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="22"/>
       <c r="D8" s="68"/>
-      <c r="E8" s="94"/>
+      <c r="E8" s="80"/>
       <c r="F8" s="69"/>
       <c r="G8" s="22"/>
       <c r="H8" s="25"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="75"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="28" t="s">
         <v>10</v>
       </c>
@@ -1917,23 +1869,23 @@
       <c r="G9" s="6"/>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="29" t="s">
         <v>45</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="76" t="s">
+      <c r="C10" s="31"/>
+      <c r="D10" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="97"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
       <c r="H10" s="25"/>
     </row>
-    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="34" t="s">
         <v>14</v>
       </c>
@@ -1945,11 +1897,11 @@
       <c r="G11" s="3"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:9" s="96" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="82" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="81" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="63" t="s">
@@ -1971,100 +1923,82 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="86"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="78"/>
+    <row r="13" spans="1:9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="78"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="73"/>
       <c r="I13" s="37"/>
     </row>
-    <row r="14" spans="1:9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="86"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="78"/>
+    <row r="14" spans="1:9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="78"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
       <c r="I14" s="37"/>
     </row>
-    <row r="15" spans="1:9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="86"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="78"/>
+    <row r="15" spans="1:9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="78"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
       <c r="I15" s="37"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="87"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="42"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="89"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="42"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="83"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="83"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
       <c r="H19" s="10"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="43" t="s">
         <v>27</v>
       </c>
@@ -2076,7 +2010,7 @@
       <c r="G21" s="44"/>
       <c r="H21" s="25"/>
     </row>
-    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -2088,57 +2022,41 @@
       <c r="G22" s="4"/>
       <c r="H22" s="46"/>
     </row>
-    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="47"/>
       <c r="C23" s="48"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
       <c r="H23" s="49" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="91"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="51"/>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="51"/>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="51"/>
       <c r="H26" s="10"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="20" t="s">
         <v>34</v>
       </c>
@@ -2150,7 +2068,7 @@
       <c r="G27" s="22"/>
       <c r="H27" s="25"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="55"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
@@ -2160,17 +2078,11 @@
       <c r="G28" s="4"/>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="52"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="20"/>
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
@@ -2197,39 +2109,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.81640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" style="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.81640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16376" width="9" style="1"/>
-    <col min="16377" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <col min="16377" max="16384" width="9.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+    <row r="1" spans="1:13" ht="18.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="100"/>
-    </row>
-    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="86"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2244,7 +2156,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
@@ -2258,7 +2170,7 @@
       <c r="I3" s="12"/>
       <c r="J3"/>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
@@ -2272,7 +2184,7 @@
       <c r="I4" s="12"/>
       <c r="J4"/>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
@@ -2283,7 +2195,7 @@
       <c r="I5" s="10"/>
       <c r="J5"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>5</v>
       </c>
@@ -2292,7 +2204,7 @@
       <c r="I6" s="10"/>
       <c r="J6"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
@@ -2303,7 +2215,7 @@
       <c r="I7" s="19"/>
       <c r="J7"/>
     </row>
-    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
         <v>7</v>
       </c>
@@ -2317,7 +2229,7 @@
       <c r="I8" s="25"/>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
         <v>8</v>
       </c>
@@ -2335,7 +2247,7 @@
       <c r="H9" s="6"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="29" t="s">
         <v>11</v>
       </c>
@@ -2346,14 +2258,14 @@
       <c r="E10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="101">
+      <c r="F10" s="87">
         <v>45189</v>
       </c>
-      <c r="G10" s="101"/>
+      <c r="G10" s="87"/>
       <c r="H10" s="33"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="34" t="s">
         <v>14</v>
       </c>
@@ -2366,7 +2278,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="61" t="s">
         <v>15</v>
       </c>
@@ -2398,7 +2310,7 @@
       <c r="L12" s="36"/>
       <c r="M12" s="36"/>
     </row>
-    <row r="13" spans="1:13" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="65">
         <v>1</v>
       </c>
@@ -2431,21 +2343,21 @@
       </c>
       <c r="J13" s="37"/>
     </row>
-    <row r="14" spans="1:13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="102" t="s">
+    <row r="14" spans="1:13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="104"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="90"/>
       <c r="J14" s="37"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="56" t="s">
         <v>24</v>
       </c>
@@ -2458,7 +2370,7 @@
       <c r="H15" s="41"/>
       <c r="I15" s="42"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
         <v>38</v>
       </c>
@@ -2471,25 +2383,25 @@
       <c r="H16" s="41"/>
       <c r="I16" s="42"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I17" s="10"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I18" s="10"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>26</v>
       </c>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="43" t="s">
         <v>27</v>
       </c>
@@ -2502,7 +2414,7 @@
       <c r="H20" s="44"/>
       <c r="I20" s="25"/>
     </row>
-    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -2515,7 +2427,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="46"/>
     </row>
-    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
@@ -2525,7 +2437,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
         <v>31</v>
       </c>
@@ -2533,7 +2445,7 @@
       <c r="C23" s="51"/>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="52" t="s">
         <v>32</v>
       </c>
@@ -2541,7 +2453,7 @@
       <c r="C24" s="51"/>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="52" t="s">
         <v>33</v>
       </c>
@@ -2549,7 +2461,7 @@
       <c r="C25" s="51"/>
       <c r="I25" s="10"/>
     </row>
-    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
         <v>34</v>
       </c>
@@ -2562,7 +2474,7 @@
       <c r="H26" s="22"/>
       <c r="I26" s="25"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="55"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
@@ -2573,11 +2485,11 @@
       <c r="H27" s="4"/>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="52"/>
       <c r="I28" s="10"/>
     </row>
-    <row r="29" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
